--- a/venture_data_template.xlsx
+++ b/venture_data_template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,17 +29,37 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="0090EE90"/>
-      <sz val="12"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0093C5FD"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00E9D5FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006EE7B7"/>
+      <sz val="11"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="007B7B7B"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
@@ -51,7 +71,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +86,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000D4F2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A2F5A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A1D96"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00065F46"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -94,10 +129,19 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -463,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -472,6 +516,10 @@
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,6 +553,26 @@
           <t>Hub_Team_Member</t>
         </is>
       </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Onboarding_Month</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Onboarding_Year</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Venture_Type</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>Program_Name</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -537,6 +605,26 @@
           <t>Meenakshi Singh</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,6 +657,26 @@
           <t>Meenakshi Singh</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Select</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -601,6 +709,26 @@
           <t>Ananya Rao</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SME</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -633,6 +761,26 @@
           <t>Ananya Rao</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -665,24 +813,64 @@
           <t>Vikram Patel</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SME</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Select</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>NOTE:</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Venture_Name must match Google Drive folder name exactly</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>One Hub Team Member per venture — their name filters the app</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Venture_Name = Google Drive folder name</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>One hub member per venture</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>e.g. January</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>e.g. 2024</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Startup or SME</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Core or Select</t>
         </is>
       </c>
     </row>
@@ -697,16 +885,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>FILE NAMING GUIDE — Name files in your Google Drive venture folders like this:</t>
         </is>
@@ -716,17 +904,17 @@
       <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Meeting Type</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Keywords to include in filename</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Keywords in filename</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Example filenames</t>
         </is>
@@ -757,12 +945,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VP1, VP2, VP3...  OR  opportunity assessment</t>
+          <t>VP1 / VP2 / VP3...  OR  opportunity assessment  OR  deep dive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VP1.pdf  /  VP2_march.pdf  /  Opportunity Assessment.pdf</t>
+          <t>VP1.pdf  /  Opportunity Assessment Transcript.pdf  /  Deep Dive.pdf</t>
         </is>
       </c>
     </row>
@@ -774,12 +962,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>panel  OR  panelist  OR  panellist</t>
+          <t>panel  OR  panelist  OR  panellist  OR  discussion with</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>panel_apr5.pdf  /  panellist_call.docx</t>
+          <t>panel_apr5.pdf  /  Discussion with Investors.pdf</t>
         </is>
       </c>
     </row>
@@ -821,7 +1009,7 @@
       <c r="A9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>WHAT THE APP EXTRACTS FROM FILES (no need to enter in Excel):</t>
         </is>
@@ -830,80 +1018,83 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓  Venture brief &amp; description</t>
+          <t xml:space="preserve">  ✓  Venture brief, problem statement, solution</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓  Problem statement &amp; solution</t>
+          <t xml:space="preserve">  ✓  Founder background</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓  Founder background</t>
+          <t xml:space="preserve">  ✓  Current stage (Idea / MVP / Growth / Scaling)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓  Current stage (Idea / MVP / Growth / Scaling)</t>
+          <t xml:space="preserve">  ✓  Current status (Active / Alumni / Stalled)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓  Current status (Active / Alumni / Stalled)</t>
+          <t xml:space="preserve">  ✓  All session dates, participants, problems, action items</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ✓  All session dates, participants, problems, action items</t>
+          <t xml:space="preserve">  ✓  Meeting effectiveness ratings</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ✓  Meeting effectiveness ratings</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>EXCEL NEEDS 10 COLUMNS:</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>EXCEL NEEDS 6 COLUMNS ONLY:</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Venture_ID  |  Venture_Name  |  Founder_Name  |  Founder_Email  |  Sector</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Venture_ID  |  Venture_Name  |  Founder_Name  |  Founder_Email  |  Sector  |  Hub_Team_Member</t>
+          <t xml:space="preserve">  Hub_Team_Member  |  Onboarding_Month  |  Onboarding_Year  |  Venture_Type  |  Program_Name</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Venture_Name must match Google Drive folder name exactly</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Hub_Team_Member: one person per venture — used to filter the app by team member</t>
+          <t>Venture_Type values:  Startup  /  SME</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Program_Name values:  Core  /  Select</t>
         </is>
       </c>
     </row>

--- a/venture_data_template.xlsx
+++ b/venture_data_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wadhwanifoundation-my.sharepoint.com/personal/meenakshi_singh_wadhwanifoundation_org/Documents/04. Advisors/2026/Accelerate Core and Select Portfolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="11_2D9350F848BCE1A3A8D867264B2786C0CAB2CC94" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D831BD64-70B2-4F40-9A0B-921C609DDBDE}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_2D9350F848BCE1A3A8D867264B2786C0CAB2CC94" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCF0F024-B4A0-4FF0-86E9-E69064EAF440}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>Qarmatek</t>
   </si>
   <si>
-    <t>Meenakshi Singh</t>
-  </si>
-  <si>
     <t>Startup</t>
   </si>
   <si>
@@ -93,9 +90,6 @@
     <t>Tailor Smart</t>
   </si>
   <si>
-    <t>Ananya Rao</t>
-  </si>
-  <si>
     <t>V004</t>
   </si>
   <si>
@@ -108,9 +102,6 @@
     <t>Vaultastic</t>
   </si>
   <si>
-    <t>Vikram Patel</t>
-  </si>
-  <si>
     <t>FILE NAMING GUIDE — Name files in your Google Drive venture folders like this:</t>
   </si>
   <si>
@@ -259,6 +250,15 @@
   </si>
   <si>
     <t>Cloud Security</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Pune</t>
   </si>
 </sst>
 </file>
@@ -758,156 +758,156 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H2">
         <v>2025</v>
       </c>
       <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
         <v>13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="H3">
         <v>2025</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" t="s">
-        <v>18</v>
-      </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="G4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H4">
         <v>2025</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H5">
         <v>2025</v>
       </c>
       <c r="I5" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" t="s">
         <v>13</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F6" t="s">
         <v>74</v>
       </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H6">
         <v>2025</v>
       </c>
       <c r="I6" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" t="s">
         <v>13</v>
-      </c>
-      <c r="J6" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -933,133 +933,133 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
